--- a/test-cases/InternSafar-Test-Cases-2026-09-24.xlsx
+++ b/test-cases/InternSafar-Test-Cases-2026-09-24.xlsx
@@ -152,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,6 +189,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,7 +628,7 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Results as of 2026-09-24. Last apply (UTC): 2026-09-24T09:07:15.975Z. Dated export: InternSafar-Test-Cases-2026-09-24.xlsx (canonical copy remains InternSafar-Test-Cases.xlsx).</t>
+          <t>Results as of 2026-09-24. Last apply (UTC): 2026-09-24T10:56:42.553Z. Dated export: InternSafar-Test-Cases-2026-09-24.xlsx (canonical copy remains InternSafar-Test-Cases.xlsx).</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1644,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -1653,7 +1656,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Applications list: tableKey candidate.applications.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: /candidate/applications</t>
+Product reference: /candidate/applications
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -1677,7 +1681,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -1745,7 +1749,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -1757,7 +1761,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Application detail sheet/dialog a11y on /candidate/applications.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: /candidate/applications</t>
+Product reference: /candidate/applications
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -1781,7 +1786,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -1849,7 +1854,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -1859,7 +1864,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate</t>
+Product reference: /candidate
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -1883,7 +1889,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -2213,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2414,7 +2420,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -2424,7 +2430,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PATCH /api/ip/employer/applications/[id]</t>
+Product reference: PATCH /api/ip/employer/applications/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -2448,7 +2455,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -2515,7 +2522,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -2525,7 +2532,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: applications/[id]</t>
+Product reference: applications/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -2617,7 +2625,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -2627,7 +2635,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/offers POST</t>
+Product reference: /api/ip/offers POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -2651,7 +2660,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -2718,7 +2727,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -2728,7 +2737,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: offers POST ownership check</t>
+Product reference: offers POST ownership check
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -2752,7 +2762,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -2820,7 +2830,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -2830,7 +2840,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/completions</t>
+Product reference: /api/ip/completions
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -2854,7 +2865,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -2921,7 +2932,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -2931,7 +2942,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/analytics</t>
+Product reference: /employer/analytics
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -2955,7 +2967,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -3022,7 +3034,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -3032,7 +3044,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: employer/applications/[id] ALLOWED</t>
+Product reference: employer/applications/[id] ALLOWED
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -3056,7 +3069,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -3123,7 +3136,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -3133,7 +3146,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: parseInterviewMeetUrl</t>
+Product reference: parseInterviewMeetUrl
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -3157,7 +3171,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -3733,9 +3747,279 @@
       </c>
       <c r="V16" s="6" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1"/>
-    <row r="19" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-09-015</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>09 Employer Postings Pipeline</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Employer profile required fields show asterisk markers</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1. Sign in as core employer.
+2. Open `/employer/profile`.
+3. Inspect labels for company name, website, work email, industry, HQ city, contact name/phone, business entity type.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Each required-for-complete field shows a visible * (required) marker. Matches REQUIRED_FOR_COMPLETE in src/lib/employerProfileComplete.js.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Playwright: journeys-employer.spec.js JOURNEY-EMP-01</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>P1 / industry QA sync</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Employer</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Core employer account</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>IS-063 employer dashboard Action center: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Employer profile completeness</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-09-016</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>09 Employer Postings Pipeline</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>New/edit posting locations use State and City fields</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>1. Employer opens `/employer/internships/new` (or edit).
+2. Locate location inputs from PostingLocationsFields.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>State and City are separate controls (not a single free-text location only). API still stores city names in locations JSONB.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>UI component: src/components/ip/PostingLocationsFields.jsx</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>P2 / industry QA sync</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Employer</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Approved employer with profile complete</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Posting locations</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-09-017</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>09 Employer Postings Pipeline</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Employer dashboard Action center sections visible</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>1. Sign in as core employer.
+2. Open `/employer`.
+3. Locate Action center.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Action center shows Action required / Upcoming style sections (data-testid=employer-action-center).</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Playwright IS-063 / journeys-employer</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>industry QA sync</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Employer</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Core employer</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>IS-063 employer dashboard Action center: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Employer dashboard</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
+    </row>
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1"/>
@@ -4708,7 +4992,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -4718,7 +5002,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PATCH /api/ip/offers/[id] status=accepted</t>
+Product reference: PATCH /api/ip/offers/[id] status=accepted
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -4742,7 +5027,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -4809,7 +5094,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -4819,7 +5104,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PATCH offers/[id] declined</t>
+Product reference: PATCH offers/[id] declined
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -4843,7 +5129,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -4911,7 +5197,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -4921,7 +5207,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: offerIsExpired + status pending check</t>
+Product reference: offerIsExpired + status pending check
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -4945,7 +5232,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -5012,7 +5299,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -5022,7 +5309,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: offers/[id] requireSession(['candidate'])</t>
+Product reference: offers/[id] requireSession(['candidate'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -5046,7 +5334,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -5114,7 +5402,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -5124,7 +5412,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/offers</t>
+Product reference: /candidate/offers
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -5148,7 +5437,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -5215,7 +5504,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -5225,7 +5514,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: offers/[id] PATCH</t>
+Product reference: offers/[id] PATCH
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -5249,7 +5539,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -5316,7 +5606,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -5326,7 +5616,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: offers/[id] candidate_id match</t>
+Product reference: offers/[id] candidate_id match
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -5350,7 +5641,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -5418,7 +5709,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -5452,7 +5743,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -5519,7 +5810,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -5553,7 +5844,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -5620,7 +5911,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -5654,7 +5945,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -5723,7 +6014,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -5757,7 +6048,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -5824,7 +6115,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -5858,7 +6149,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -7027,7 +7318,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -7037,7 +7328,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/messages /api/ip/messages/threads</t>
+Product reference: /candidate/messages /api/ip/messages/threads
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -7061,7 +7353,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -7129,7 +7421,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -7139,7 +7431,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: threads/[id] PATCH</t>
+Product reference: threads/[id] PATCH
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -7163,7 +7456,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -7232,7 +7525,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -7243,7 +7536,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Notifications page: /candidate/notifications.
-Product reference: /candidate/notifications /api/ip/nav-badges</t>
+Product reference: /candidate/notifications /api/ip/nav-badges
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -7267,7 +7561,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -7335,7 +7629,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -7345,7 +7639,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/notifications</t>
+Product reference: /candidate/notifications
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -7369,7 +7664,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -7436,7 +7731,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -7446,7 +7741,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: messages/threads POST</t>
+Product reference: messages/threads POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -7470,7 +7766,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -7537,7 +7833,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -7547,7 +7843,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: threads/[id] POST</t>
+Product reference: threads/[id] POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -7571,7 +7868,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -7638,7 +7935,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -7648,7 +7945,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: threads/[id] membership check</t>
+Product reference: threads/[id] membership check
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -7672,7 +7970,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -8387,7 +8685,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -8397,7 +8695,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/referral</t>
+Product reference: /candidate/referral
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -8421,7 +8720,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -8488,7 +8787,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -8523,7 +8822,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -8591,7 +8890,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -8626,7 +8925,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -8956,7 +9255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9156,7 +9455,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -9166,7 +9465,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin</t>
+Product reference: /superadmin
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -9190,7 +9490,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -9260,7 +9560,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -9270,7 +9570,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: POST /api/ip/superadmin/form-registrations</t>
+Product reference: POST /api/ip/superadmin/form-registrations
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -9294,7 +9595,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -9363,7 +9664,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -9373,7 +9674,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: form-registrations reject</t>
+Product reference: form-registrations reject
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -9397,7 +9699,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -9465,7 +9767,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -9475,7 +9777,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/form-registrations</t>
+Product reference: /superadmin/form-registrations
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -9499,7 +9802,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -9568,7 +9871,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -9578,7 +9881,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PATCH /api/ip/superadmin/employers/[id]</t>
+Product reference: PATCH /api/ip/superadmin/employers/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -9602,7 +9906,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -9671,7 +9975,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -9681,7 +9985,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: employers/[id] ALLOWED statuses</t>
+Product reference: employers/[id] ALLOWED statuses
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -9705,7 +10010,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -9772,7 +10077,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -9782,7 +10087,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: superadmin/employers/[id]</t>
+Product reference: superadmin/employers/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -9806,7 +10112,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -9875,7 +10181,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -9885,7 +10191,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/requests</t>
+Product reference: /superadmin/requests
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -9909,7 +10216,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -9976,7 +10283,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -9986,7 +10293,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/requests</t>
+Product reference: /superadmin/requests
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -10010,7 +10318,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -10078,7 +10386,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -10088,7 +10396,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/documents</t>
+Product reference: /superadmin/documents
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -10112,7 +10421,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -10180,7 +10489,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -10190,7 +10499,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/postings</t>
+Product reference: /superadmin/postings
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -10214,7 +10524,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -10282,7 +10592,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -10292,7 +10602,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/promotions</t>
+Product reference: /superadmin/promotions
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -10316,7 +10627,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -10384,7 +10695,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -10394,7 +10705,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/viral/process-due</t>
+Product reference: /api/ip/viral/process-due
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -10418,7 +10730,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -10488,7 +10800,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -10498,7 +10810,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/login-report GET /api/ip/superadmin/login-report</t>
+Product reference: /superadmin/login-report GET /api/ip/superadmin/login-report
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -10522,7 +10835,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -10590,7 +10903,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -10600,7 +10913,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/login-report</t>
+Product reference: /superadmin/login-report
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -10624,7 +10938,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -10692,7 +11006,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -10702,7 +11016,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/messages</t>
+Product reference: /superadmin/messages
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
@@ -10726,7 +11041,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -10795,7 +11110,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -10805,7 +11120,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/feature-ideas</t>
+Product reference: /superadmin/feature-ideas
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
@@ -10829,7 +11145,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -10896,7 +11212,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -10906,7 +11222,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/superadmin/export-audit</t>
+Product reference: /api/ip/superadmin/export-audit
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M20" s="6" t="n"/>
@@ -10930,7 +11247,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -10997,7 +11314,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -11007,7 +11324,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: form-registrations requireSession superadmin</t>
+Product reference: form-registrations requireSession superadmin
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M21" s="6" t="n"/>
@@ -11098,7 +11416,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -11108,7 +11426,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: superadmin/employers/[id]</t>
+Product reference: superadmin/employers/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M22" s="6" t="n"/>
@@ -11132,7 +11451,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -11200,7 +11519,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -11210,7 +11529,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: superadmin/requests POST</t>
+Product reference: superadmin/requests POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M23" s="6" t="n"/>
@@ -11234,7 +11554,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -11342,7 +11662,100 @@
       </c>
       <c r="V24" s="6" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-14-023</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>14 SuperAdmin Ops</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SuperAdmin re-applying same posting status skips notify/email</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>1. As SuperAdmin, pick a posting already `published`.
+2. PATCH `/api/ip/superadmin/postings` with status=published again.
+3. Inspect JSON: skipped increments; changed stays 0 for that id.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>When current_status === target status, API returns ok with changed=false and does not call notifyUser.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Playwright journeys-superadmin.spec.js JOURNEY-SA-01</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>P1 / industry QA sync</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>SuperAdmin</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>At least one published internship</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>JOURNEY-SA-01 postings page + same-status publish skips change: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Posting moderation</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr"/>
+    </row>
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
@@ -11748,7 +12161,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -11782,7 +12195,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -11852,7 +12265,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -11886,7 +12299,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -11954,7 +12367,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -11988,7 +12401,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -12055,7 +12468,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -12089,7 +12502,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -12156,7 +12569,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -12190,7 +12603,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -13746,7 +14159,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -13781,7 +14194,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -13848,7 +14261,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -13882,7 +14295,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -13949,7 +14362,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -13983,7 +14396,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -14418,9 +14831,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>&lt;&lt; Back to Index</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Coverage Matrix — synced 2026-09-24 (Obsolete/Manual/Automated)</t>
         </is>
       </c>
     </row>
@@ -15085,7 +15498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15286,7 +15699,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -15296,7 +15709,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/profile</t>
+Product reference: /employer/profile
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -15320,7 +15734,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -15389,7 +15803,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -15399,7 +15813,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/employer/documents</t>
+Product reference: /api/ip/employer/documents
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -15423,7 +15838,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -15491,7 +15906,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -15501,7 +15916,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: employerEthics + profile PUT</t>
+Product reference: employerEthics + profile PUT
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -15525,7 +15941,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -15593,7 +16009,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -15603,7 +16019,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer</t>
+Product reference: /employer
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -15627,7 +16044,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -15697,7 +16114,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -15707,7 +16124,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: POST /api/ip/employer/internships</t>
+Product reference: POST /api/ip/employer/internships
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -15731,7 +16149,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -15799,7 +16217,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -15811,7 +16229,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Publish costs 50 points; draft does not.
 Publish DT: points&gt;=50 × approved × profile_complete × not already published.
-Product reference: chargePublishPoints</t>
+Product reference: chargePublishPoints
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -15835,7 +16254,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -15903,7 +16322,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -15913,7 +16332,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships POST</t>
+Product reference: internships POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -15937,7 +16357,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -16004,7 +16424,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -16014,7 +16434,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships POST approval_status</t>
+Product reference: internships POST approval_status
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -16038,7 +16459,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -16105,7 +16526,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -16115,7 +16536,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships POST profileGate</t>
+Product reference: internships POST profileGate
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -16139,7 +16561,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -16206,7 +16628,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -16216,7 +16638,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships POST</t>
+Product reference: internships POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -16240,7 +16663,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -16308,7 +16731,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -16318,7 +16741,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PUT/DELETE /api/ip/employer/internships/[id]</t>
+Product reference: PUT/DELETE /api/ip/employer/internships/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -16342,7 +16766,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -16411,7 +16835,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -16421,7 +16845,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/internships/new  [id]/edit</t>
+Product reference: /employer/internships/new  [id]/edit
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -16445,7 +16870,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -16512,7 +16937,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -16522,7 +16947,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships/[id] loadOwned</t>
+Product reference: internships/[id] loadOwned
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -16546,7 +16972,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -16616,7 +17042,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -16628,7 +17054,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Full-page profile at /employer/candidates/[id] (not a modal).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: /employer/candidates POST .../invite</t>
+Product reference: /employer/candidates POST .../invite
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -16652,7 +17079,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -16721,7 +17148,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -16732,7 +17159,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Search filters + invite from full-page profile or search row.
-Product reference: /employer/candidates</t>
+Product reference: /employer/candidates
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -16756,7 +17184,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -16825,7 +17253,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -16835,7 +17263,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/messages</t>
+Product reference: /employer/messages
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
@@ -16859,7 +17288,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -16927,7 +17356,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -16937,7 +17366,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/offers</t>
+Product reference: /employer/offers
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
@@ -16961,7 +17391,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -17030,7 +17460,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -17040,7 +17470,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/viral /api/ip/viral /api/ip/promotions</t>
+Product reference: /employer/viral /api/ip/viral /api/ip/promotions
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M20" s="6" t="n"/>
@@ -17064,7 +17495,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -17133,7 +17564,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -17143,7 +17574,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /employer/referral</t>
+Product reference: /employer/referral
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M21" s="6" t="n"/>
@@ -17167,7 +17599,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -17236,7 +17668,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -17247,7 +17679,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Employer notifications: /employer/notifications.
-Product reference: /employer/notifications</t>
+Product reference: /employer/notifications
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M22" s="6" t="n"/>
@@ -17271,7 +17704,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -17340,7 +17773,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -17350,7 +17783,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships/[id] PUT existing.status !== published</t>
+Product reference: internships/[id] PUT existing.status !== published
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M23" s="6" t="n"/>
@@ -17374,7 +17808,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -17442,7 +17876,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -17452,7 +17886,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: internships/[id] PUT republish</t>
+Product reference: internships/[id] PUT republish
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M24" s="6" t="n"/>
@@ -17476,7 +17911,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -17543,7 +17978,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -17554,7 +17989,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Invite requires internshipId.
-Product reference: candidates/[id]/invite</t>
+Product reference: candidates/[id]/invite
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M25" s="6" t="n"/>
@@ -17578,7 +18014,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -17645,7 +18081,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -17656,7 +18092,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Cannot invite on another employer’s posting.
-Product reference: invite ownership</t>
+Product reference: invite ownership
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M26" s="6" t="n"/>
@@ -17680,7 +18117,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -17748,7 +18185,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -17782,7 +18219,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -17849,7 +18286,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -17883,7 +18320,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -17953,7 +18390,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -17988,7 +18425,7 @@
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -18058,7 +18495,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -18093,7 +18530,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -18161,7 +18598,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -18195,7 +18632,7 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -18227,20 +18664,19 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Home and register expose real Google OAuth; password login still works</t>
+          <t>Home email/password only; register exposes Google OAuth; password login still works</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>1. Open `/` — confirm Sign in with Google is present when GOOGLE_* is configured.
-2. Click it and confirm redirect to accounts.google.com with matching redirect_uri.
-3. Return; sign in with email/password + captcha — lands on role home.
-4. Open /register/candidate — Google control still present.</t>
+          <t>1. Open `/` — confirm #email/#password and no Google button.
+2. Open `/register/candidate` — confirm Sign up with Google.
+3. Sign in with core candidate email/password.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>GoogleProvider is enabled when secrets exist. Credentials login remains independent. Supersedes obsolete 'home has no Google button / GoogleLoginDisabled-only' assumption.</t>
+          <t>Home never offers Google login. Register starts Google OAuth for verification/create. Credentials login remains independent.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -18265,7 +18701,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -18294,7 +18730,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>Automated (partial) + Manual consent</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -18362,7 +18798,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -18396,7 +18832,7 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -18467,7 +18903,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -18573,7 +19009,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -18607,7 +19043,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -18676,7 +19112,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -18711,7 +19147,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -18778,7 +19214,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -18812,7 +19248,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -19161,7 +19597,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -19258,7 +19694,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -19355,7 +19791,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -19452,7 +19888,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -19548,7 +19984,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
@@ -19644,7 +20080,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -19740,7 +20176,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
@@ -19838,7 +20274,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
@@ -19881,7 +20317,99 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-18-047</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>18 Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Unsubscribe page without token shows Link not valid</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>1. Open `/unsubscribe` with no query token.
+2. Read page copy.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Shows 'Link not valid' (or equivalent) and does not crash.</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>Playwright IS-055</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="6" t="n"/>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>industry QA sync</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="n"/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>IS-055 unsubscribe page handles missing token: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>Email unsubscribe</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr"/>
+    </row>
     <row r="50" ht="15" customHeight="1"/>
     <row r="51" ht="15" customHeight="1"/>
     <row r="52" ht="15" customHeight="1"/>
@@ -20263,7 +20791,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -20274,7 +20802,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Home sign-in uses #email and #password.
-Product reference: /  (IpSignInLanding)</t>
+Product reference: /  (IpSignInLanding)
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -20298,7 +20827,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -20368,7 +20897,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -20379,7 +20908,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: /login redirects to `/` and keeps query params.
-Product reference: /login → /</t>
+Product reference: /login → /
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -20403,7 +20933,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -20472,7 +21002,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -20483,7 +21013,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP captcha: correct, blank, wrong, stale token, missing token.
-Product reference: /</t>
+Product reference: /
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -20507,7 +21038,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -20576,7 +21107,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -20586,7 +21117,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /how-it-works /guidelines /help</t>
+Product reference: /how-it-works /guidelines /help
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -20610,7 +21142,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -20679,7 +21211,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -20689,7 +21221,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /register</t>
+Product reference: /register
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -20713,7 +21246,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -20782,7 +21315,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -20792,7 +21325,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /r/[code]</t>
+Product reference: /r/[code]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -20816,7 +21350,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -20885,7 +21419,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -20895,7 +21429,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /app</t>
+Product reference: /app
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -20919,7 +21454,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -20986,7 +21521,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -21020,7 +21555,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -21090,7 +21625,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -21100,7 +21635,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /register*</t>
+Product reference: /register*
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -21558,7 +22094,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -21570,7 +22106,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Candidate/employer: Gmail+ cores on `/` with captcha.
 EP captcha: correct, blank, wrong, stale token, missing token.
-Product reference: / + NextAuth Credentials POST /api/auth/[...nextauth]</t>
+Product reference: / + NextAuth Credentials POST /api/auth/[...nextauth]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -21594,7 +22131,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -21662,7 +22199,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -21674,7 +22211,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: src/lib/auth.js authorize()</t>
+Product reference: src/lib/auth.js authorize()
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -21698,7 +22236,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -21765,7 +22303,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -21777,7 +22315,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: auth.js</t>
+Product reference: auth.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -21801,7 +22340,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -21870,7 +22409,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -21880,7 +22419,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: auth.js SESSION_SHORT_SEC / SESSION_LONG_SEC</t>
+Product reference: auth.js SESSION_SHORT_SEC / SESSION_LONG_SEC
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -21904,7 +22444,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -21971,7 +22511,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -21982,7 +22522,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: auth.js</t>
+Product reference: auth.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -22006,7 +22547,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -22075,7 +22616,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -22085,7 +22626,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: auth.js active / form_approval_status</t>
+Product reference: auth.js active / form_approval_status
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -22109,7 +22651,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -22177,7 +22719,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -22187,7 +22729,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: auth.js queryWithRetry</t>
+Product reference: auth.js queryWithRetry
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -22211,7 +22754,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -22281,7 +22824,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -22292,7 +22835,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: /forgot-password POST /api/ip/auth/password-reset/request</t>
+Product reference: /forgot-password POST /api/ip/auth/password-reset/request
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -22316,7 +22860,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -22384,7 +22928,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -22396,7 +22940,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 EP captcha: correct, blank, wrong, stale token, missing token.
-Product reference: password-reset/request</t>
+Product reference: password-reset/request
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -22420,7 +22965,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -22490,7 +23035,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -22501,7 +23046,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
-Product reference: POST /api/ip/auth/password-reset/confirm</t>
+Product reference: POST /api/ip/auth/password-reset/confirm
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -22525,7 +23071,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -22596,7 +23142,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -22607,7 +23153,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: /account POST /api/ip/account/2fa  auth.js 2FA branch</t>
+Product reference: /account POST /api/ip/account/2fa  auth.js 2FA branch
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -22631,7 +23178,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -22700,7 +23247,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -22710,7 +23257,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: ipTwoFactor + auth.js</t>
+Product reference: ipTwoFactor + auth.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -22734,7 +23282,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -22802,7 +23350,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -22813,7 +23361,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
-Product reference: /api/ip/account/2fa actions start-disable / confirm-disable</t>
+Product reference: /api/ip/account/2fa actions start-disable / confirm-disable
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -22837,7 +23386,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -22907,7 +23456,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -22918,7 +23467,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: SuperAdmin: placementhubsupport@gmail.com on /superadmin/login (#sa-email, #sa-password).
-Product reference: /superadmin/login</t>
+Product reference: /superadmin/login
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -22942,7 +23492,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -23012,7 +23562,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -23022,7 +23572,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /account GET/DELETE /api/ip/account/sessions</t>
+Product reference: /account GET/DELETE /api/ip/account/sessions
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -23046,7 +23597,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -23116,7 +23667,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -23128,7 +23679,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Account password change requires upper + digit + special.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
-Product reference: POST /api/ip/auth/change-password</t>
+Product reference: POST /api/ip/auth/change-password
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
@@ -23152,7 +23704,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -23221,7 +23773,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -23233,7 +23785,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Weak new password on /account is rejected.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
-Product reference: change-password</t>
+Product reference: change-password
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
@@ -23257,7 +23810,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -23324,7 +23877,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -23334,7 +23887,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/account/2fa</t>
+Product reference: /api/ip/account/2fa
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M20" s="6" t="n"/>
@@ -23358,7 +23912,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -23425,7 +23979,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -23435,7 +23989,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/account/2fa</t>
+Product reference: /api/ip/account/2fa
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M21" s="6" t="n"/>
@@ -23459,7 +24014,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -23527,7 +24082,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -23540,7 +24095,8 @@
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 EP captcha: correct, blank, wrong, stale token, missing token.
-Product reference: /forgot-password</t>
+Product reference: /forgot-password
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M22" s="6" t="n"/>
@@ -23564,7 +24120,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -23633,7 +24189,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -23643,7 +24199,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: recordLoginEvent + login-report</t>
+Product reference: recordLoginEvent + login-report
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M23" s="6" t="n"/>
@@ -23667,7 +24224,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -23737,7 +24294,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -23749,7 +24306,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Captcha must be solved on home login.
 EP captcha: correct, blank, wrong, stale token, missing token.
-Product reference: simpleCaptcha + auth.js</t>
+Product reference: simpleCaptcha + auth.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M24" s="6" t="n"/>
@@ -23773,7 +24331,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -23898,19 +24456,20 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Home Sign in with Google reaches accounts.google.com with matching redirect_uri</t>
+          <t>Candidate register Sign up with Google reaches accounts.google.com with matching redirect_uri</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>1. Open `/` signed out.
-2. Click Sign in with Google (button.ip-gemini-google-btn).
-3. Stop on Google accounts URL; inspect client_id and redirect_uri.</t>
+          <t>1. Open `/register/candidate` signed out.
+2. Click Sign up with Google (button.ip-crg-google-btn).
+3. Stop on Google accounts URL; inspect client_id and redirect_uri.
+4. Confirm home `/` has no Google login button.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Browser reaches accounts.google.com. redirect_uri is `{origin}/api/auth/callback/google` matching the app origin.</t>
+          <t>Browser reaches accounts.google.com. redirect_uri is `{origin}/api/auth/callback/google` matching the app origin. Home `/` has email/password only (no Sign in with Google).</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -23935,12 +24494,13 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Completing Google consent is optional. Playwright: qa/tests/google-auth.spec.js</t>
+          <t>Playwright: qa/tests/google-auth.spec.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M26" s="6" t="n"/>
@@ -23964,7 +24524,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Automated (google-auth + QA remaining suite)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -23996,18 +24556,19 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>GoogleAccountNotLinked shows friendly message</t>
+          <t>GoogleLoginDisabled / GoogleAccountNotLinked show friendly message</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>1. Open `/?error=GoogleAccountNotLinked`.
-2. Read the banner/message.</t>
+          <t>1. Open `/?error=GoogleLoginDisabled`.
+2. Open `/?error=GoogleAccountNotLinked`.
+3. Read the banner/message.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Friendly copy about no linked account / sign up with Google — not a raw NextAuth dump.</t>
+          <t>Friendly copy that Google sign-in is not available — use email/password. Not a raw NextAuth dump.</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -24032,12 +24593,13 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Playwright google-auth.spec.js / regression.spec.js</t>
+          <t>Playwright google-auth.spec.js / regression.spec.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M27" s="6" t="n"/>
@@ -24129,12 +24691,13 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>Demo candidate from qa helpers</t>
+          <t>Demo candidate from qa helpers
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M28" s="6" t="n"/>
@@ -24158,7 +24721,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>Automated (auth / QA)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -24190,7 +24753,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Linked Google account Sign in with Google opens a portal session</t>
+          <t>[Obsolete] Linked Google account Sign in with Google opens a portal session</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -24220,9 +24783,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -24233,7 +24796,8 @@
       <c r="L29" s="6" t="inlineStr">
         <is>
           <t>Added 2026-09-15 to cover linked home Google login. Automated start/unlinked covered by TC-IS-02-024/025.
-Manual verify Pass after fresh Google register + linked home Sign in.</t>
+Manual verify Pass after fresh Google register + linked home Sign in.
+Obsolete 2026-09-24: Google login on home removed; portal session via home Google is unreachable.</t>
         </is>
       </c>
       <c r="M29" s="6" t="n"/>
@@ -24259,9 +24823,9 @@
           <t>Manual Pass 2026-09-15: deleted lawsonlclintern@gmail.com, re-registered as candidate via Google, then home Sign in with Google opened /candidate session (linked identity).</t>
         </is>
       </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>Manual</t>
+      <c r="T29" s="16" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -24697,7 +25261,8 @@
 Excluded from automated QA — manual registration/account-creation testing only.
 Aligned 2026-09-15: clarified registration vs linked home Google login.
 Manual verify Pass on Vercel after Google register + temp password login.
-Expected/Actual aligned 2026-09-16 to live post-create sessionEstablished behavior (OAuth hop still ?gv= only).</t>
+Expected/Actual aligned 2026-09-16 to live post-create sessionEstablished behavior (OAuth hop still ?gv= only).
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -24789,7 +25354,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -24801,7 +25366,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: authRegisterRules.isGmailAddress
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -24893,7 +25459,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -24905,7 +25471,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -25000,7 +25567,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -25017,7 +25584,8 @@
 Product reference: register-candidate path=form  /superadmin/form-registrations
 Excluded from automated QA — manual registration/account-creation testing only.
 Manual/API case — no form path on /register/candidate UI after Gemini redesign.
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -25110,7 +25678,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -25122,7 +25690,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: /register/candidate
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -25146,7 +25715,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -25229,7 +25798,8 @@
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate + pointsEconomy.REFERRAL_POINTS=25
 Excluded from automated QA — manual registration/account-creation testing only.
-Manual verify Pass after ref-preserve fix (alert + +25 on referrer).</t>
+Manual verify Pass after ref-preserve fix (alert + +25 on referrer).
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -25338,7 +25908,8 @@
 Product reference: form-registrations + ipReferralCredit
 Excluded from automated QA — manual registration/account-creation testing only.
 Manual/API — candidate form path has no UI.
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -25446,7 +26017,8 @@
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: POST /api/ip/auth/register-employer  approval_status=pending
 Excluded from automated QA — manual registration/account-creation testing only.
-Manual Pass 2026-09-16: one-run with sibling case; publish gated on SA approval (profile complete first).</t>
+Manual Pass 2026-09-16: one-run with sibling case; publish gated on SA approval (profile complete first).
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -25538,7 +26110,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -25550,7 +26122,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-employer domainsMatch
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -25641,7 +26214,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -25654,7 +26227,8 @@
 Product reference: register-employer
 Excluded from automated QA — manual registration/account-creation testing only.
 API-only — domain UI no longer has a website field (Google derives domain).
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -25758,7 +26332,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Product reference: register-employer manualRequest=true  /superadmin/requests
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -25849,7 +26424,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -25860,7 +26435,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Product reference: register-employer forceManual
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -25963,7 +26539,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-employer
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -26054,7 +26631,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -26066,7 +26643,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: authRegisterRules GMAIL_DOMAINS
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -26170,7 +26748,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate self_referral
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -26261,7 +26840,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -26273,7 +26852,8 @@
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
@@ -26365,7 +26945,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -26380,7 +26960,8 @@
 Product reference: register-candidate captcha before insert
 Excluded from automated QA — manual registration/account-creation testing only.
 API-only — no candidate form UI.
-Excluded from automated QA — manual registration/account-creation testing only.</t>
+Excluded from automated QA — manual registration/account-creation testing only.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
@@ -26473,7 +27054,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -26730,7 +27311,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Home Google sign-in without register intent: unlinked account -&gt; GoogleAccountNotLinked</t>
+          <t>[Obsolete] Home Google sign-in without register intent: unlinked account -&gt; GoogleAccountNotLinked</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -26760,9 +27341,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -26772,7 +27353,8 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Rewritten 2026-09-15: product now allows linked Google login on home; unlinked no-intent path uses GoogleAccountNotLinked. GoogleLoginDisabled is UI-map only and is not the current auth callback outcome. Manual (needs real Google consent). Companion success path: TC-IS-02-027.</t>
+          <t>Rewritten 2026-09-15: product now allows linked Google login on home; unlinked no-intent path uses GoogleAccountNotLinked. GoogleLoginDisabled is UI-map only and is not the current auth callback outcome. Manual (needs real Google consent). Companion success path: TC-IS-02-027.
+Obsolete 2026-09-24: Home has no Google control; use GoogleLoginDisabled / register Google paths instead.</t>
         </is>
       </c>
       <c r="M23" s="6" t="n"/>
@@ -26794,9 +27376,9 @@
           <t>{"status":200,"note":"Automated: unlinked error route reachable. Completing live Google consent with an unlinked account remains manual."}</t>
         </is>
       </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>Manual</t>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -27401,7 +27983,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -27411,7 +27993,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PortalShell unauthenticated → loginHref</t>
+Product reference: PortalShell unauthenticated → loginHref
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -27435,7 +28018,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -27504,7 +28087,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -27514,7 +28097,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: PortalShell + role layouts</t>
+Product reference: PortalShell + role layouts
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -27538,7 +28122,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -27607,7 +28191,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -27617,7 +28201,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: requireSession(['candidate'])</t>
+Product reference: requireSession(['candidate'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -27641,7 +28226,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -27709,7 +28294,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -27719,7 +28304,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: requireSession(['employer'])</t>
+Product reference: requireSession(['employer'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -27743,7 +28329,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -27811,7 +28397,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -27821,7 +28407,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: requireSession(['superadmin'])</t>
+Product reference: requireSession(['superadmin'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -27845,7 +28432,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -27913,7 +28500,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -27923,7 +28510,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /ideas ideas/layout.js</t>
+Product reference: /ideas ideas/layout.js
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -27947,7 +28535,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -28014,7 +28602,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -28024,7 +28612,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: requireSession(['employer'])</t>
+Product reference: requireSession(['employer'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -28048,7 +28637,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -28115,7 +28704,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -28125,7 +28714,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: requireSession(['candidate'])</t>
+Product reference: requireSession(['candidate'])
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -28149,7 +28739,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -28217,7 +28807,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -28227,7 +28817,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: superadmin/layout.js pathname exception</t>
+Product reference: superadmin/layout.js pathname exception
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -28251,7 +28842,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -28684,7 +29275,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -28719,7 +29310,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -28787,7 +29378,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -28821,7 +29412,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -28889,7 +29480,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -28924,7 +29515,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -28993,7 +29584,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -29028,7 +29619,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -29096,7 +29687,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -29130,7 +29721,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -29366,7 +29957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29569,12 +30160,13 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>QASkills: EP complete vs incomplete; BVA phone blank vs invalid national number. Tabs today: 1. Basics &amp; Contact, 2. Academic &amp; Skills, 3. Work Readiness, 4. Privacy &amp; Photo, 5. Endorsements (Read-Only). Wizard steps 1–3 on first visit. Legacy ID annotation if present stays.</t>
+          <t>QASkills: EP complete vs incomplete; BVA phone blank vs invalid national number. Tabs today: 1. Basics &amp; Contact, 2. Academic &amp; Skills, 3. Work Readiness, 4. Privacy &amp; Photo, 5. Endorsements (Read-Only). Wizard steps 1–3 on first visit. Legacy ID annotation if present stays.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -29598,7 +30190,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -29669,7 +30261,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -29680,7 +30272,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Photo/privacy on tab 4; academics via /api/ip/candidate/academics.
-Product reference: candidate/profile EDITABLE_FIELDS</t>
+Product reference: candidate/profile EDITABLE_FIELDS
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -29704,7 +30297,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -29772,7 +30365,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -29783,7 +30376,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Incomplete-profile banner on /candidate and /candidate/profile.
-Product reference: ProfileReminderBanner + /api/ip/profile-reminder</t>
+Product reference: ProfileReminderBanner + /api/ip/profile-reminder
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -29807,7 +30401,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -29875,7 +30469,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -29886,7 +30480,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Export: GET /api/ip/candidate/export from profile.
-Product reference: /api/ip/candidate/export</t>
+Product reference: /api/ip/candidate/export
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -29910,7 +30505,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -29978,7 +30573,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -30013,7 +30608,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -30407,7 +31002,99 @@
       </c>
       <c r="V11" s="6" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1"/>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-06-010</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>06 Candidate Profile</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Candidate profile has Save draft control</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>1. Candidate opens `/candidate/profile`.
+2. Locate Save draft control.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Save draft (or Save draft &amp; exit) button is visible.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Playwright IS-062</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>industry QA sync</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Core candidate</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>IS-062 profile has Save draft &amp; exit: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Profile draft</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
+    </row>
     <row r="13" ht="15" customHeight="1"/>
     <row r="14" ht="15" customHeight="1"/>
     <row r="15" ht="15" customHeight="1"/>
@@ -30625,7 +31312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30825,7 +31512,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -30835,7 +31522,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/internships</t>
+Product reference: /candidate/internships
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n"/>
@@ -30859,7 +31547,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -30928,7 +31616,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -30939,7 +31627,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Browse filters include minMatch, minValidation, quick chips; tableKey candidate.internships.
-Product reference: GET /api/ip/candidate/internships</t>
+Product reference: GET /api/ip/candidate/internships
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M4" s="6" t="n"/>
@@ -30963,7 +31652,7 @@
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -31033,7 +31722,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -31044,7 +31733,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Correction vs old checklist: Cards/List toggle, Filters panel, Saved views bar; mobile layout.
-Product reference: /candidate/internships</t>
+Product reference: /candidate/internships
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -31068,7 +31758,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -31137,7 +31827,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -31147,7 +31837,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /api/ip/candidate/saved</t>
+Product reference: /api/ip/candidate/saved
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -31171,7 +31862,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -31238,7 +31929,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -31248,7 +31939,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: /candidate/internships/[id]</t>
+Product reference: /candidate/internships/[id]
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -31272,7 +31964,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -31341,7 +32033,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -31352,7 +32044,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: POST /api/ip/candidate/applications POINTS_PER_APPLICATION=5</t>
+Product reference: POST /api/ip/candidate/applications POINTS_PER_APPLICATION=5
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -31376,7 +32069,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -31443,7 +32136,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -31454,7 +32147,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: applications route dupe check</t>
+Product reference: applications route dupe check
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -31478,7 +32172,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -31545,7 +32239,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -31556,7 +32250,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: applications POST</t>
+Product reference: applications POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -31580,7 +32275,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -31648,7 +32343,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -31659,7 +32354,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: applications screening</t>
+Product reference: applications screening
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -31683,7 +32379,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -31751,7 +32447,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -31762,7 +32458,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: POINTS_PER_APPLICATION</t>
+Product reference: POINTS_PER_APPLICATION
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -31786,7 +32483,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -31854,12 +32551,13 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>QASkills EP: no skills listed vs partial overlap vs full. Bands from ipScoreBands.scoreBand. Legacy annotation unchanged.</t>
+          <t>QASkills EP: no skills listed vs partial overlap vs full. Bands from ipScoreBands.scoreBand. Legacy annotation unchanged.
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -31883,7 +32581,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -31950,7 +32648,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -31961,7 +32659,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: applications POST</t>
+Product reference: applications POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -31985,7 +32684,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -32052,7 +32751,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -32063,7 +32762,8 @@
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
-Product reference: applications POST</t>
+Product reference: applications POST
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -32087,7 +32787,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -32155,7 +32855,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -32165,7 +32865,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: candidate/internships matchesLocation</t>
+Product reference: candidate/internships matchesLocation
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -32189,7 +32890,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -32257,7 +32958,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:07:15.975Z</t>
+          <t>2026-09-24T10:56:42.553Z</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -32267,7 +32968,8 @@
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
 Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer shreekar.nyayapathi23+2@vit.edu / Admin@123; SA placementhubsupport@gmail.com / Admin@123. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin on /superadmin/login (#sa-email, #sa-password).
-Product reference: matchesWorkMode</t>
+Product reference: matchesWorkMode
+Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -32291,7 +32993,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>Manual (sibling has scripts/run-ip-checklist-qa.mjs coverage for many AUTH/PERM IDs — must be remapped to TC-IS-* before treating as green)</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -32871,8 +33573,194 @@
       </c>
       <c r="V23" s="6" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-07-022</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>07 Browse Save Apply</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Internship detail exposes Report listing control</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>1. Candidate session.
+2. Open a visible internship detail.
+3. Find Report button.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Report control is visible on detail page.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Playwright IS-061</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>industry QA sync</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>At least one published internship visible to candidate</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>IS-061 internship detail exposes Report listing control: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Internship detail</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>TC-IS-07-023</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>07 Browse Save Apply</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Browse filters include start date options</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>1. Candidate opens `/candidate/internships`.
+2. Open Filter drawer.
+3. Confirm Start date label and option e.g. Starts within 30 days.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Start date filter present in browse drawer.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Ready for QA</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:56:42.553Z</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Playwright IS-064</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>industry QA sync</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Core candidate</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>IS-064 browse filters include start date: Playwright regression passed</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Browse filters</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr"/>
+    </row>
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
